--- a/Assets/Data/DataTable/99_String_Table.xlsx
+++ b/Assets/Data/DataTable/99_String_Table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9E3182-C476-4739-B8FB-A0B89397F016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0232AA85-1FDC-457F-998F-6FE8B7CA2E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -825,7 +825,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="168">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1288,10 +1288,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CHARACTER_NAME_1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CHARACTER_NAME_1001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1300,14 +1296,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_PASSIVE_NAME_3000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MONSTER_NAME_2000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MONSTER_NAME_2001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1465,6 +1453,34 @@
   </si>
   <si>
     <t>CHAOS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHARACTER_NAME_1003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MONSTER_NAME_2004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_NAME_3003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_ACTIVE_NAME_5004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>액티브 스킬 이름 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_ACTIVE_DESC_6004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>액티브 스킬 설명 4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4375,7 +4391,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4201226D-AF20-433D-BB3C-B7FD91A16A54}">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.25" bestFit="1" customWidth="1"/>
@@ -4517,7 +4533,7 @@
         <v>1003</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="F7" s="25" t="s">
         <v>100</v>
@@ -4539,7 +4555,7 @@
         <v>2001</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F8" s="25" t="s">
         <v>101</v>
@@ -4561,7 +4577,7 @@
         <v>2002</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F9" s="25" t="s">
         <v>102</v>
@@ -4583,7 +4599,7 @@
         <v>2003</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F10" s="25" t="s">
         <v>103</v>
@@ -4605,7 +4621,7 @@
         <v>2004</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="F11" s="25" t="s">
         <v>104</v>
@@ -4627,7 +4643,7 @@
         <v>3001</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F12" s="25" t="s">
         <v>105</v>
@@ -4649,7 +4665,7 @@
         <v>3002</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F13" s="25" t="s">
         <v>106</v>
@@ -4671,7 +4687,7 @@
         <v>3003</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="F14" s="25" t="s">
         <v>107</v>
@@ -4693,7 +4709,7 @@
         <v>4001</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F15" s="25" t="s">
         <v>108</v>
@@ -4715,7 +4731,7 @@
         <v>4002</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F16" s="25" t="s">
         <v>109</v>
@@ -4724,7 +4740,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="24">
-        <f t="shared" ref="A17:A39" si="1">(B17*1000000) + (C17*10000) + D17</f>
+        <f t="shared" ref="A17:A41" si="1">(B17*1000000) + (C17*10000) + D17</f>
         <v>99044003</v>
       </c>
       <c r="B17" s="24">
@@ -4737,7 +4753,7 @@
         <v>4003</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F17" s="25" t="s">
         <v>110</v>
@@ -4759,7 +4775,7 @@
         <v>5001</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F18" s="25" t="s">
         <v>111</v>
@@ -4781,7 +4797,7 @@
         <v>5002</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F19" s="25" t="s">
         <v>112</v>
@@ -4803,7 +4819,7 @@
         <v>5003</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F20" s="25" t="s">
         <v>113</v>
@@ -4813,29 +4829,29 @@
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="24">
         <f t="shared" si="1"/>
-        <v>99066001</v>
+        <v>99055004</v>
       </c>
       <c r="B21" s="24">
         <v>99</v>
       </c>
       <c r="C21" s="30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21" s="24">
-        <v>6001</v>
+        <v>5004</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="G21" s="25"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="24">
         <f t="shared" si="1"/>
-        <v>99066002</v>
+        <v>99066001</v>
       </c>
       <c r="B22" s="24">
         <v>99</v>
@@ -4844,20 +4860,20 @@
         <v>6</v>
       </c>
       <c r="D22" s="24">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G22" s="25"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="24">
         <f t="shared" si="1"/>
-        <v>99066003</v>
+        <v>99066002</v>
       </c>
       <c r="B23" s="24">
         <v>99</v>
@@ -4866,68 +4882,64 @@
         <v>6</v>
       </c>
       <c r="D23" s="24">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G23" s="25"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="24">
         <f t="shared" si="1"/>
-        <v>99077001</v>
+        <v>99066003</v>
       </c>
       <c r="B24" s="24">
         <v>99</v>
       </c>
       <c r="C24" s="30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D24" s="24">
-        <v>7001</v>
+        <v>6003</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="G24" s="25" t="s">
-        <v>152</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="G24" s="25"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="24">
         <f t="shared" si="1"/>
-        <v>99077002</v>
+        <v>99066004</v>
       </c>
       <c r="B25" s="24">
         <v>99</v>
       </c>
       <c r="C25" s="30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25" s="24">
-        <v>7002</v>
+        <v>6004</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="G25" s="25" t="s">
-        <v>153</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="G25" s="25"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="24">
         <f t="shared" si="1"/>
-        <v>99077003</v>
+        <v>99077001</v>
       </c>
       <c r="B26" s="24">
         <v>99</v>
@@ -4936,22 +4948,22 @@
         <v>7</v>
       </c>
       <c r="D26" s="24">
-        <v>7003</v>
+        <v>7001</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="G26" s="25" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="24">
         <f t="shared" si="1"/>
-        <v>99077004</v>
+        <v>99077002</v>
       </c>
       <c r="B27" s="24">
         <v>99</v>
@@ -4960,22 +4972,22 @@
         <v>7</v>
       </c>
       <c r="D27" s="24">
-        <v>7004</v>
+        <v>7002</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G27" s="25" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="24">
         <f t="shared" si="1"/>
-        <v>99077005</v>
+        <v>99077003</v>
       </c>
       <c r="B28" s="24">
         <v>99</v>
@@ -4984,22 +4996,22 @@
         <v>7</v>
       </c>
       <c r="D28" s="24">
-        <v>7005</v>
+        <v>7003</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G28" s="25" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="24">
         <f t="shared" si="1"/>
-        <v>99077006</v>
+        <v>99077004</v>
       </c>
       <c r="B29" s="24">
         <v>99</v>
@@ -5008,22 +5020,22 @@
         <v>7</v>
       </c>
       <c r="D29" s="24">
-        <v>7006</v>
+        <v>7004</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G29" s="25" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="24">
         <f t="shared" si="1"/>
-        <v>99077007</v>
+        <v>99077005</v>
       </c>
       <c r="B30" s="24">
         <v>99</v>
@@ -5032,22 +5044,22 @@
         <v>7</v>
       </c>
       <c r="D30" s="24">
-        <v>7007</v>
+        <v>7005</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G30" s="25" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="24">
         <f t="shared" si="1"/>
-        <v>99077008</v>
+        <v>99077006</v>
       </c>
       <c r="B31" s="24">
         <v>99</v>
@@ -5056,22 +5068,22 @@
         <v>7</v>
       </c>
       <c r="D31" s="24">
-        <v>7008</v>
+        <v>7006</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G31" s="25" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="24">
         <f t="shared" si="1"/>
-        <v>99077009</v>
+        <v>99077007</v>
       </c>
       <c r="B32" s="24">
         <v>99</v>
@@ -5080,22 +5092,22 @@
         <v>7</v>
       </c>
       <c r="D32" s="24">
-        <v>7009</v>
+        <v>7007</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G32" s="25" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="24">
         <f t="shared" si="1"/>
-        <v>99077010</v>
+        <v>99077008</v>
       </c>
       <c r="B33" s="24">
         <v>99</v>
@@ -5104,22 +5116,22 @@
         <v>7</v>
       </c>
       <c r="D33" s="24">
-        <v>7010</v>
+        <v>7008</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="F33" s="32" t="s">
-        <v>97</v>
+        <v>142</v>
+      </c>
+      <c r="F33" s="25" t="s">
+        <v>89</v>
       </c>
       <c r="G33" s="25" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="24">
         <f t="shared" si="1"/>
-        <v>99077011</v>
+        <v>99077009</v>
       </c>
       <c r="B34" s="24">
         <v>99</v>
@@ -5128,22 +5140,22 @@
         <v>7</v>
       </c>
       <c r="D34" s="24">
-        <v>7011</v>
+        <v>7009</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G34" s="25" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="24">
         <f t="shared" si="1"/>
-        <v>99077012</v>
+        <v>99077010</v>
       </c>
       <c r="B35" s="24">
         <v>99</v>
@@ -5152,22 +5164,22 @@
         <v>7</v>
       </c>
       <c r="D35" s="24">
-        <v>7012</v>
+        <v>7010</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="F35" s="25" t="s">
-        <v>92</v>
+        <v>145</v>
+      </c>
+      <c r="F35" s="32" t="s">
+        <v>97</v>
       </c>
       <c r="G35" s="25" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="24">
         <f t="shared" si="1"/>
-        <v>99077013</v>
+        <v>99077011</v>
       </c>
       <c r="B36" s="24">
         <v>99</v>
@@ -5176,45 +5188,65 @@
         <v>7</v>
       </c>
       <c r="D36" s="24">
-        <v>7013</v>
+        <v>7011</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G36" s="25" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="24">
         <f t="shared" si="1"/>
-        <v>99000000</v>
+        <v>99077012</v>
       </c>
       <c r="B37" s="24">
         <v>99</v>
       </c>
-      <c r="C37" s="30"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
+      <c r="C37" s="30">
+        <v>7</v>
+      </c>
+      <c r="D37" s="24">
+        <v>7012</v>
+      </c>
+      <c r="E37" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="F37" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="G37" s="25" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="24">
         <f t="shared" si="1"/>
-        <v>99000000</v>
+        <v>99077013</v>
       </c>
       <c r="B38" s="24">
         <v>99</v>
       </c>
-      <c r="C38" s="30"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
+      <c r="C38" s="30">
+        <v>7</v>
+      </c>
+      <c r="D38" s="24">
+        <v>7013</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="F38" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="G38" s="25" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="24">
@@ -5229,6 +5261,34 @@
       <c r="E39" s="24"/>
       <c r="F39" s="25"/>
       <c r="G39" s="25"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="24">
+        <f t="shared" si="1"/>
+        <v>99000000</v>
+      </c>
+      <c r="B40" s="24">
+        <v>99</v>
+      </c>
+      <c r="C40" s="30"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="24">
+        <f t="shared" si="1"/>
+        <v>99000000</v>
+      </c>
+      <c r="B41" s="24">
+        <v>99</v>
+      </c>
+      <c r="C41" s="30"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
